--- a/modules/40_q3/figures/editable/origin_templates/data/24_Si验证偏差瀑布图.xlsx
+++ b/modules/40_q3/figures/editable/origin_templates/data/24_Si验证偏差瀑布图.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="1" r:id="Rb16140c411e54291"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="1" r:id="R9f0fbd40e6844443"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,30 +13,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
-    <x:numFmt numFmtId="200" formatCode="@"/>
-    <x:numFmt numFmtId="201" formatCode="0.000000"/>
-  </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF222222"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="宋体"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Times New Roman"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:name val="Times New Roman"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
   <x:fills count="3">
@@ -52,175 +43,37 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="2">
     <x:border/>
     <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
       <x:left style="thin">
-        <x:color rgb="FFE7EEF5"/>
+        <x:color rgb="FFD9E2F3"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:left>
-      <x:bottom style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFE7EEF5"/>
+        <x:color rgb="FFD9E2F3"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FFE7EEF5"/>
+        <x:color rgb="FFD9E2F3"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFE7EEF5"/>
+        <x:color rgb="FFD9E2F3"/>
       </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:top>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -424,53 +277,53 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="16" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="6" t="str">
         <x:v>验证项目(分类X)</x:v>
       </x:c>
-      <x:c r="B1" s="17" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>相对差异(%)(Y)</x:v>
       </x:c>
-      <x:c r="C1" s="18" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>判读(标签)</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="25" t="str">
-        <x:v>单角度厚度差</x:v>
-      </x:c>
-      <x:c r="B2" s="27" t="n">
-        <x:v>3.371183352077082</x:v>
-      </x:c>
-      <x:c r="C2" s="29" t="str">
-        <x:v>低于5%一致性界限</x:v>
+      <x:c r="A2" s="2" t="str">
+        <x:v>10度与15度厚度差</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="n">
+        <x:v>1.8794989427728903</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="str">
+        <x:v>独立角度差异</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="25" t="str">
-        <x:v>联合与平均差</x:v>
-      </x:c>
-      <x:c r="B3" s="27" t="n">
-        <x:v>2.2726963983090815</x:v>
-      </x:c>
-      <x:c r="C3" s="29" t="str">
-        <x:v>低于5%一致性界限</x:v>
+      <x:c r="A3" s="2" t="str">
+        <x:v>Airy平均与冻结结果差</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="str">
+        <x:v>冻结结果一致</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="26" t="str">
-        <x:v>实角与复法向差</x:v>
-      </x:c>
-      <x:c r="B4" s="28" t="n">
-        <x:v>9.408030999792902e-7</x:v>
-      </x:c>
-      <x:c r="C4" s="30" t="str">
-        <x:v>折射角口径敏感性</x:v>
+      <x:c r="A4" s="2" t="str">
+        <x:v>Q3阈值语境</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="str">
+        <x:v>工程语境，不参与正式模型选择</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
